--- a/activity_sports_waivers_forms/023_high_intensity_functional_training_registration--activity_sports_waivers_forms.xlsx
+++ b/activity_sports_waivers_forms/023_high_intensity_functional_training_registration--activity_sports_waivers_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>strength_training</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Strength Training</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>program_type_choices</t>
+          <t>program_level_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>program_level_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>training_frequency_choices</t>
+          <t>workout_duration_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>workout_duration_choices</t>
+          <t>training_time_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>training_time_choices</t>
+          <t>training_days_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>training_days_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>high_blood_pressure</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High Blood Pressure</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>epilepsy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Epilepsy</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>epilepsy</t>
+          <t>pregnancy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Pregnancy</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pregnancy</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pregnancy</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>injuries_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>back_injuries</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Back Injuries</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>back_injuries</t>
+          <t>knee_injuries</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Back Injuries</t>
+          <t>Knee Injuries</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>knee_injuries</t>
+          <t>hip_injuries</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Knee Injuries</t>
+          <t>Hip Injuries</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1896,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hip_injuries</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hip Injuries</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>injuries_choices</t>
+          <t>medical_devices_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>walker</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Walker</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>walker</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wheelchair</t>
+          <t>hearing_device</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wheelchair</t>
+          <t>Hearing Device</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>hearing_device</t>
+          <t>vision_device</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hearing Device</t>
+          <t>Vision Device</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>vision_device</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vision Device</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>medical_devices_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medication_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medication 1</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>medication_1</t>
+          <t>medication_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Medication 1</t>
+          <t>Medication 2</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>medication_2</t>
+          <t>medication_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Medication 2</t>
+          <t>Medication 3</t>
         </is>
       </c>
     </row>
@@ -2049,27 +2049,10 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>medication_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
-        <is>
-          <t>Medication 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>medications_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
